--- a/survey_templates/029_public_composting_petition_form--survey_templates.xlsx
+++ b/survey_templates/029_public_composting_petition_form--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -757,8 +757,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="46" customWidth="1" min="2" max="2"/>
-    <col width="46" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -786,12 +786,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'value':_'student'}</t>
+          <t>student</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'value': 'Student'}</t>
+          <t>Student</t>
         </is>
       </c>
     </row>
@@ -803,12 +803,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'value':_'teacher'}</t>
+          <t>teacher</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'value': 'Teacher'}</t>
+          <t>Teacher</t>
         </is>
       </c>
     </row>
@@ -820,12 +820,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'value':_'parent'}</t>
+          <t>parent</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'value': 'Parent'}</t>
+          <t>Parent</t>
         </is>
       </c>
     </row>
@@ -837,12 +837,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'value':_'community_leader'}</t>
+          <t>community_leader</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'value': 'Community Leader'}</t>
+          <t>Community Leader</t>
         </is>
       </c>
     </row>
@@ -854,12 +854,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_5,_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 5, 'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -871,12 +871,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_1,_'value':_'community_composting'}</t>
+          <t>community_composting</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 1, 'value': 'Community Composting'}</t>
+          <t>Community Composting</t>
         </is>
       </c>
     </row>
@@ -888,12 +888,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_2,_'value':_'food_waste_reduction'}</t>
+          <t>food_waste_reduction</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 2, 'value': 'Food Waste Reduction'}</t>
+          <t>Food Waste Reduction</t>
         </is>
       </c>
     </row>
@@ -905,12 +905,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_3,_'value':_'urban_agriculture'}</t>
+          <t>urban_agriculture</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 3, 'value': 'Urban Agriculture'}</t>
+          <t>Urban Agriculture</t>
         </is>
       </c>
     </row>
@@ -922,12 +922,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_4,_'value':_'education_and_outreach'}</t>
+          <t>education_and_outreach</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 4, 'value': 'Education and Outreach'}</t>
+          <t>Education and Outreach</t>
         </is>
       </c>
     </row>
@@ -939,12 +939,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_5,_'value':_'community_garden'}</t>
+          <t>community_garden</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 5, 'value': 'Community Garden'}</t>
+          <t>Community Garden</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_6,_'value':_'community_policy'}</t>
+          <t>community_policy</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 6, 'value': 'Community Policy'}</t>
+          <t>Community Policy</t>
         </is>
       </c>
     </row>
